--- a/artfynd/A 11115-2026 artfynd.xlsx
+++ b/artfynd/A 11115-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131745763</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131746011</v>
       </c>
       <c r="B3" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>131745869</v>
       </c>
       <c r="B4" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11115-2026 artfynd.xlsx
+++ b/artfynd/A 11115-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>131745763</v>
       </c>
       <c r="B2" t="n">
-        <v>93180</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,14 +781,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131746011</v>
+        <v>131745869</v>
       </c>
       <c r="B3" t="n">
-        <v>93180</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605463</v>
+        <v>605373</v>
       </c>
       <c r="R3" t="n">
-        <v>6554361</v>
+        <v>6554442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,9 +875,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -895,14 +895,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131745869</v>
+        <v>131746011</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605373</v>
+        <v>605463</v>
       </c>
       <c r="R4" t="n">
-        <v>6554442</v>
+        <v>6554361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,9 +989,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,6 +1006,324 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131750985</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Trehörningen , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>605300</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6554468</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131750978</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trehörningen , Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>605300</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6554468</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131751505</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dammkärret , Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>605480</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6554281</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11115-2026 artfynd.xlsx
+++ b/artfynd/A 11115-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131745763</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131745869</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131746011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131750985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131750978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,8 +1354,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131751505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>